--- a/static/data/exports/Retro_UK_AE_2017.xlsx
+++ b/static/data/exports/Retro_UK_AE_2017.xlsx
@@ -3400,7 +3400,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -21577,7 +21577,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D287" t="n">
@@ -40214,7 +40214,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D540" t="n">
